--- a/app/src/main/java/com/example/methodmesh/modules/nfc/docs/example_odk_nfc_tag_wipe.xlsx
+++ b/app/src/main/java/com/example/methodmesh/modules/nfc/docs/example_odk_nfc_tag_wipe.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R018ecad45b63441a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R8d4afa0764764d9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R18a1d557fad94fb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rffce5953bfc9492e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R1906ae2e93274a63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R8c56f04229974952"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -32,7 +32,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -44,6 +44,11 @@
         <x:fgColor rgb="FF164E63"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2E8F0"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -51,7 +56,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="8">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -64,6 +69,10 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -598,28 +607,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" hidden="0" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="7" t="str">
         <x:v>form_title</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="7" t="str">
         <x:v>form_id</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="7" t="str">
         <x:v>version</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="7" t="str">
         <x:v>instance_name</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="36" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>nfc_tag_wipe</x:v>
+        <x:v>NFC Tag Wipe</x:v>
       </x:c>
       <x:c r="B2" s="3" t="str">
         <x:v>nfc_tag_wipe</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>2026072701</x:v>
+        <x:v>2026090703</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>concat('nfc_tag_wipe - ', ${start})</x:v>
